--- a/docs/2/software-tech/Учебный_план_Технология_разработки_ПО.xlsx
+++ b/docs/2/software-tech/Учебный_план_Технология_разработки_ПО.xlsx
@@ -195,12 +195,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Программная инженерия и жизненный цикл»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Программная инженерия заменяет стихийное написание кода управляемым процессом. Разберём фазы жизненного цикла и цену ошибки на каждой из них.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Программная инженерия и жизненный цикл</t>
+          <t xml:space="preserve">жизненный цикл, фаза, артефакт, стоимость ошибки, программная инженерия</t>
         </is>
       </c>
     </row>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Модели жизненного цикла»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Водопад, итерационная и V-модель по-разному распределяют риск и обратную связь. Разберём, когда какая модель уместна и чем платят за гибкость.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Модели жизненного цикла</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t xml:space="preserve">водопад, итерация, V-модель, прототип, риск</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3-4</t>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Анализ требований; User stories и критерии приёмки.</t>
+          <t xml:space="preserve">Разбираете описание задачи на требования, оформляете user stories и критерии приёмки. Сдаёте список историй с приоритетами и проверяемыми критериями.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ требований, User stories и критерии приёмки</t>
+          <t xml:space="preserve">требование, user story, критерий приёмки, приоритет, актор</t>
         </is>
       </c>
     </row>
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Agile и Scrum»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Agile задаёт ценности и короткие циклы, Scrum добавляет роли, события и артефакты. Разберём спринт по шагам и точки, где принимаются решения.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agile и Scrum</t>
+          <t xml:space="preserve">Agile, спринт, бэклог, скрам-мастер, ретроспектива, инкремент</t>
         </is>
       </c>
     </row>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Требования и user stories»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Требование становится рабочим, когда его можно проверить и оценить по трудозатратам. Разберём структуру user story, критерии приёмки и INVEST.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Требования и user stories</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t xml:space="preserve">user story, INVEST, критерий приёмки, нефункциональное требование, трассируемость</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Use case; Диаграмма классов.</t>
+          <t xml:space="preserve">Строите диаграмму прецедентов для выбранной системы и диаграмму классов с атрибутами и связями. Сдаёте две модели и пояснение к каждой связи.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use case, Диаграмма классов</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t xml:space="preserve">прецедент, актор, класс, ассоциация, кратность, граница системы</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Анализ предметной области»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Анализ предметной области отделяет сущности и правила бизнеса от будущего интерфейса. Разберём, как из интервью и документов получается рабочая модель.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ предметной области</t>
+          <t xml:space="preserve">предметная область, сущность, правило бизнеса, глоссарий, границы системы</t>
         </is>
       </c>
     </row>
@@ -405,12 +405,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «ER-модель»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Строите ER-модель предметной области с сущностями, атрибутами и связями, проверяете её на нормальные формы. Сдаёте диаграмму и пояснение ключей.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ER-модель</t>
+          <t xml:space="preserve">сущность, связь, первичный ключ, внешний ключ, нормальная форма</t>
         </is>
       </c>
     </row>
@@ -435,12 +435,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Проектирование архитектуры»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Архитектура задаёт крупные части системы и правила их взаимодействия. Разберём слои, модули и компромисс между связностью и связанностью.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проектирование архитектуры</t>
+          <t xml:space="preserve">архитектура, слой, модуль, связанность, контракт, клиент-сервер</t>
         </is>
       </c>
     </row>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Макет интерфейса»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете макет экранов для сценария пользователя и проверяете его на согласованность. Сдаёте макет с описанием элементов и обоснованием раскладки.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Макет интерфейса</t>
+          <t xml:space="preserve">макет, сетка, элемент интерфейса, сценарий, прототип</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «UML и моделирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">UML задаёт набор нотаций, и диаграмму выбирают по вопросу, а не по привычке. Разберём структурные и поведенческие диаграммы и их связь с кодом.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UML и моделирование</t>
+          <t xml:space="preserve">UML, нотация, диаграмма классов, диаграмма последовательности, модель</t>
         </is>
       </c>
     </row>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Проектирование данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Схема данных определяет, какие запросы будут быстрыми, а какие потребуют обходов. Разберём нормализацию, индексы и денормализацию под нагрузку.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проектирование данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t xml:space="preserve">нормализация, индекс, денормализация, транзакция, целостность</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15-16</t>
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Настройка Git; Ветвление и merge.</t>
+          <t xml:space="preserve">Настраиваете репозиторий Git, ведёте работу в ветках и сливаете изменения, разбирая конфликт вручную. Сдаёте репозиторий с историей и описанием конфликта.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настройка Git, Ветвление и merge</t>
+          <t xml:space="preserve">git init, ветка, merge, конфликт, коммит, .gitignore</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Интерфейс и UX»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">UX отвечает за путь пользователя к цели, интерфейс за конкретные экраны. Разберём эвристики удобства, обратную связь и обработку ошибок ввода.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интерфейс и UX</t>
+          <t xml:space="preserve">UX, юзабилити, эвристика, обратная связь, состояние ошибки</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Code review»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Проверяете чужой код по чек-листу и оставляете замечания с приоритетом и предложением. Сдаёте список замечаний и итоговое решение по пул-реквесту.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Code review</t>
+          <t xml:space="preserve">пул-реквест, замечание, чек-лист, стиль кода, приоритет</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Стандарты кодирования»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Единый стиль снижает цену чтения и ревью, а линтер делает его проверяемым. Разберём PEP 8, именование, длину функций и автоматические проверки.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стандарты кодирования</t>
+          <t xml:space="preserve">PEP 8, линтер, форматер, именование, документация функции</t>
         </is>
       </c>
     </row>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Git и ветвление»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Ветка в Git это указатель на коммит, поэтому создание ветки почти бесплатно. Разберём модель коммитов, слияние, rebase и стратегии ветвления.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Git и ветвление</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t xml:space="preserve">коммит, ветка, rebase, merge, конфликт, удалённый репозиторий</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21-22</t>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Тест-кейсы; Автоматизация проверок.</t>
+          <t xml:space="preserve">Пишете тест-кейсы на функцию и превращаете часть из них в автотесты с проверкой результата. Сдаёте набор тест-кейсов и запускаемый набор тестов.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест-кейсы, Автоматизация проверок</t>
+          <t xml:space="preserve">тест-кейс, граничное значение, автотест, assert, покрытие</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Code review»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Ревью ловит дефекты раньше тестов и распространяет знание по команде. Разберём порядок просмотра, размер изменения и тон замечаний.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Code review</t>
+          <t xml:space="preserve">ревью, пул-реквест, замечание, чек-лист, размер изменения</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Отладка»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Ищете причину падения программы по трассировке и точкам останова, проверяете гипотезы. Сдаёте исправленный код и разбор причины дефекта.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отладка</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t xml:space="preserve">трассировка, точка останова, гипотеза, воспроизведение, лог</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование ПО»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Тестирование показывает наличие дефектов, но не доказывает их отсутствие. Разберём уровни, виды и пирамиду тестов, а также когда нужен ручной прогон.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование ПО</t>
+          <t xml:space="preserve">уровень тестирования, регрессия, пирамида тестов, тест-план, дефект</t>
         </is>
       </c>
     </row>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Документация»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Оформляете документацию проекта: руководство запуска, описание API и журнал изменений. Сдаёте документ, по которому новый человек запускает проект.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документация</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t xml:space="preserve">руководство, API, docstring, журнал изменений, версия</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27</t>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Отладка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Отладка начинается с устойчивого воспроизведения дефекта, а не с правки кода. Разберём бинарный поиск причины, логирование и типичные ловушки.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отладка</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t xml:space="preserve">воспроизведение, бинарный поиск, логирование, точка останова, стек вызовов</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Документирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Документация делится на пользовательскую, эксплуатационную и внутреннюю, и у каждой свой читатель. Разберём структуру документа и поддержание его в актуальном виде.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t xml:space="preserve">документация, руководство пользователя, регламент, шаблон, актуальность</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29-30</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сборка проекта; Релиз.</t>
+          <t xml:space="preserve">Настраиваете сборку проекта, прогоняете проверки и выпускаете версию с тегом и журналом изменений. Сдаёте собранный артефакт и описание релиза.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сборка проекта, Релиз</t>
+          <t xml:space="preserve">сборка, зависимости, версия, тег, артефакт, журнал изменений</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сборка и релиз»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сборка превращает исходники в готовый артефакт, релиз закрепляет версию и доводит её до пользователя. Разберём версионирование, конвейер и откат.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сборка и релиз</t>
+          <t xml:space="preserve">конвейер, семантическое версионирование, артефакт, тег, откат</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Внедрение»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Внедрение переносит систему в рабочую среду и меняет привычки пользователей. Разберём миграцию данных, обучение и план перехода без простоя.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Внедрение</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t xml:space="preserve">внедрение, миграция данных, опытная эксплуатация, обучение, откат</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33-34</t>
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Внедрение; Сопровождение.</t>
+          <t xml:space="preserve">Разворачиваете систему на стенде, переносите данные и оформляете регламент сопровождения. Сдаёте работающий стенд, план миграции и инструкцию.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Внедрение, Сопровождение</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">развёртывание, миграция, регламент, обращение, резервная копия</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1035,16 +1035,16 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сопровождение»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сопровождение охватывает исправления, доработки и поддержку пользователей после сдачи. Разберём классификацию обращений, приоритеты и метрики службы поддержки.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сопровождение</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t xml:space="preserve">сопровождение, обращение, SLA, приоритет, регрессия, релиз</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Оценка качества»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Оцениваете учебный проект по метрикам качества и находите слабые места в коде и документации. Сдаёте отчёт с метриками, дефектами и планом улучшений.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка качества</t>
+          <t xml:space="preserve">метрика, сложность, дублирование, чек-лист, технический долг</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Оценка качества и рисков»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Качество измеряют метриками продукта и процесса, а риски оценивают по вероятности и последствиям. Разберём реестр рисков и выбор мер.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка качества и рисков</t>
+          <t xml:space="preserve">метрика, риск, вероятность, реестр рисков, технический долг</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговый проект»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете итоговый проект: требования, модель, код, тесты, документацию и релиз. Сдаёте репозиторий с историей и защиту принятых решений.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговый проект</t>
+          <t xml:space="preserve">итоговый проект, репозиторий, защита, релиз, документация</t>
         </is>
       </c>
     </row>

--- a/docs/2/software-tech/Учебный_план_Технология_разработки_ПО.xlsx
+++ b/docs/2/software-tech/Учебный_план_Технология_разработки_ПО.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>3420</v>
+        <v>76</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>

--- a/docs/2/software-tech/Учебный_план_Технология_разработки_ПО.xlsx
+++ b/docs/2/software-tech/Учебный_план_Технология_разработки_ПО.xlsx
@@ -234,40 +234,40 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Анализ требований; User stories и критерии приёмки</t>
+          <t xml:space="preserve">Лекция 3. Agile и Scrum</t>
         </is>
       </c>
       <c r="D8" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете описание задачи на требования, оформляете user stories и критерии приёмки. Сдаёте список историй с приоритетами и проверяемыми критериями.</t>
+          <t xml:space="preserve">Agile задаёт ценности и короткие циклы, Scrum добавляет роли, события и артефакты. Разберём спринт по шагам и точки, где принимаются решения.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">требование, user story, критерий приёмки, приоритет, актор</t>
+          <t xml:space="preserve">Agile, спринт, бэклог, скрам-мастер, ретроспектива, инкремент</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Agile и Scrum</t>
+          <t xml:space="preserve">Лекция 4. Требования и user stories</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,79 +285,79 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agile задаёт ценности и короткие циклы, Scrum добавляет роли, события и артефакты. Разберём спринт по шагам и точки, где принимаются решения.</t>
+          <t xml:space="preserve">Требование становится рабочим, когда его можно проверить и оценить по трудозатратам. Разберём структуру user story, критерии приёмки и INVEST.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agile, спринт, бэклог, скрам-мастер, ретроспектива, инкремент</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">user story, INVEST, критерий приёмки, нефункциональное требование, трассируемость</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5-6</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Требования и user stories</t>
+          <t xml:space="preserve">Практика 1. Анализ требований; User stories и критерии приёмки</t>
         </is>
       </c>
       <c r="D10" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Требование становится рабочим, когда его можно проверить и оценить по трудозатратам. Разберём структуру user story, критерии приёмки и INVEST.</t>
+          <t xml:space="preserve">Разбираете описание задачи на требования, оформляете user stories и критерии приёмки. Сдаёте список историй с приоритетами и проверяемыми критериями.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">user story, INVEST, критерий приёмки, нефункциональное требование, трассируемость</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t xml:space="preserve">требование, user story, критерий приёмки, приоритет, актор</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Use case; Диаграмма классов</t>
+          <t xml:space="preserve">Лекция 5. Анализ предметной области</t>
         </is>
       </c>
       <c r="D11" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строите диаграмму прецедентов для выбранной системы и диаграмму классов с атрибутами и связями. Сдаёте две модели и пояснение к каждой связи.</t>
+          <t xml:space="preserve">Анализ предметной области отделяет сущности и правила бизнеса от будущего интерфейса. Разберём, как из интервью и документов получается рабочая модель.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">прецедент, актор, класс, ассоциация, кратность, граница системы</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t xml:space="preserve">предметная область, сущность, правило бизнеса, глоссарий, границы системы</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Анализ предметной области</t>
+          <t xml:space="preserve">Лекция 6. Проектирование архитектуры</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,29 +375,29 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анализ предметной области отделяет сущности и правила бизнеса от будущего интерфейса. Разберём, как из интервью и документов получается рабочая модель.</t>
+          <t xml:space="preserve">Архитектура задаёт крупные части системы и правила их взаимодействия. Разберём слои, модули и компромисс между связностью и связанностью.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">предметная область, сущность, правило бизнеса, глоссарий, границы системы</t>
+          <t xml:space="preserve">архитектура, слой, модуль, связанность, контракт, клиент-сервер</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. ER-модель</t>
+          <t xml:space="preserve">Лекция 7. UML и моделирование</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -405,42 +405,42 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строите ER-модель предметной области с сущностями, атрибутами и связями, проверяете её на нормальные формы. Сдаёте диаграмму и пояснение ключей.</t>
+          <t xml:space="preserve">UML задаёт набор нотаций, и диаграмму выбирают по вопросу, а не по привычке. Разберём структурные и поведенческие диаграммы и их связь с кодом.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сущность, связь, первичный ключ, внешний ключ, нормальная форма</t>
+          <t xml:space="preserve">UML, нотация, диаграмма классов, диаграмма последовательности, модель</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10-11</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Проектирование архитектуры</t>
+          <t xml:space="preserve">Практика 2. Use case; Диаграмма классов</t>
         </is>
       </c>
       <c r="D14" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Архитектура задаёт крупные части системы и правила их взаимодействия. Разберём слои, модули и компромисс между связностью и связанностью.</t>
+          <t xml:space="preserve">Строите диаграмму прецедентов для выбранной системы и диаграмму классов с атрибутами и связями. Сдаёте две модели и пояснение к каждой связи.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">архитектура, слой, модуль, связанность, контракт, клиент-сервер</t>
+          <t xml:space="preserve">прецедент, актор, класс, ассоциация, кратность, граница системы</t>
         </is>
       </c>
     </row>
@@ -452,12 +452,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Макет интерфейса</t>
+          <t xml:space="preserve">Лекция 8. Проектирование данных</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете макет экранов для сценария пользователя и проверяете его на согласованность. Сдаёте макет с описанием элементов и обоснованием раскладки.</t>
+          <t xml:space="preserve">Схема данных определяет, какие запросы будут быстрыми, а какие потребуют обходов. Разберём нормализацию, индексы и денормализацию под нагрузку.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">макет, сетка, элемент интерфейса, сценарий, прототип</t>
+          <t xml:space="preserve">нормализация, индекс, денормализация, транзакция, целостность</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. UML и моделирование</t>
+          <t xml:space="preserve">Практика 3. ER-модель</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UML задаёт набор нотаций, и диаграмму выбирают по вопросу, а не по привычке. Разберём структурные и поведенческие диаграммы и их связь с кодом.</t>
+          <t xml:space="preserve">Строите ER-модель предметной области с сущностями, атрибутами и связями, проверяете её на нормальные формы. Сдаёте диаграмму и пояснение ключей.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UML, нотация, диаграмма классов, диаграмма последовательности, модель</t>
+          <t xml:space="preserve">сущность, связь, первичный ключ, внешний ключ, нормальная форма</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Проектирование данных</t>
+          <t xml:space="preserve">Лекция 9. Интерфейс и UX</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,19 +525,19 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Схема данных определяет, какие запросы будут быстрыми, а какие потребуют обходов. Разберём нормализацию, индексы и денормализацию под нагрузку.</t>
+          <t xml:space="preserve">UX отвечает за путь пользователя к цели, интерфейс за конкретные экраны. Разберём эвристики удобства, обратную связь и обработку ошибок ввода.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">нормализация, индекс, денормализация, транзакция, целостность</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t xml:space="preserve">UX, юзабилити, эвристика, обратная связь, состояние ошибки</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -547,27 +547,27 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Настройка Git; Ветвление и merge</t>
+          <t xml:space="preserve">Практика 4. Макет интерфейса</t>
         </is>
       </c>
       <c r="D18" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настраиваете репозиторий Git, ведёте работу в ветках и сливаете изменения, разбирая конфликт вручную. Сдаёте репозиторий с историей и описанием конфликта.</t>
+          <t xml:space="preserve">Собираете макет экранов для сценария пользователя и проверяете его на согласованность. Сдаёте макет с описанием элементов и обоснованием раскладки.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">git init, ветка, merge, конфликт, коммит, .gitignore</t>
+          <t xml:space="preserve">макет, сетка, элемент интерфейса, сценарий, прототип</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Интерфейс и UX</t>
+          <t xml:space="preserve">Лекция 10. Стандарты кодирования</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,29 +585,29 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UX отвечает за путь пользователя к цели, интерфейс за конкретные экраны. Разберём эвристики удобства, обратную связь и обработку ошибок ввода.</t>
+          <t xml:space="preserve">Единый стиль снижает цену чтения и ревью, а линтер делает его проверяемым. Разберём PEP 8, именование, длину функций и автоматические проверки.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UX, юзабилити, эвристика, обратная связь, состояние ошибки</t>
+          <t xml:space="preserve">PEP 8, линтер, форматер, именование, документация функции</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Code review</t>
+          <t xml:space="preserve">Лекция 11. Git и ветвление</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,42 +615,42 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверяете чужой код по чек-листу и оставляете замечания с приоритетом и предложением. Сдаёте список замечаний и итоговое решение по пул-реквесту.</t>
+          <t xml:space="preserve">Ветка в Git это указатель на коммит, поэтому создание ветки почти бесплатно. Разберём модель коммитов, слияние, rebase и стратегии ветвления.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">пул-реквест, замечание, чек-лист, стиль кода, приоритет</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t xml:space="preserve">коммит, ветка, rebase, merge, конфликт, удалённый репозиторий</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18-19</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Стандарты кодирования</t>
+          <t xml:space="preserve">Практика 5. Настройка Git; Ветвление и merge</t>
         </is>
       </c>
       <c r="D21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Единый стиль снижает цену чтения и ревью, а линтер делает его проверяемым. Разберём PEP 8, именование, длину функций и автоматические проверки.</t>
+          <t xml:space="preserve">Настраиваете репозиторий Git, ведёте работу в ветках и сливаете изменения, разбирая конфликт вручную. Сдаёте репозиторий с историей и описанием конфликта.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEP 8, линтер, форматер, именование, документация функции</t>
+          <t xml:space="preserve">git init, ветка, merge, конфликт, коммит, .gitignore</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Git и ветвление</t>
+          <t xml:space="preserve">Лекция 12. Code review</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,19 +675,19 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ветка в Git это указатель на коммит, поэтому создание ветки почти бесплатно. Разберём модель коммитов, слияние, rebase и стратегии ветвления.</t>
+          <t xml:space="preserve">Ревью ловит дефекты раньше тестов и распространяет знание по команде. Разберём порядок просмотра, размер изменения и тон замечаний.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">коммит, ветка, rebase, merge, конфликт, удалённый репозиторий</t>
+          <t xml:space="preserve">ревью, пул-реквест, замечание, чек-лист, размер изменения</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Тест-кейсы; Автоматизация проверок</t>
+          <t xml:space="preserve">Практика 6. Code review</t>
         </is>
       </c>
       <c r="D23" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пишете тест-кейсы на функцию и превращаете часть из них в автотесты с проверкой результата. Сдаёте набор тест-кейсов и запускаемый набор тестов.</t>
+          <t xml:space="preserve">Проверяете чужой код по чек-листу и оставляете замечания с приоритетом и предложением. Сдаёте список замечаний и итоговое решение по пул-реквесту.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">тест-кейс, граничное значение, автотест, assert, покрытие</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t xml:space="preserve">пул-реквест, замечание, чек-лист, стиль кода, приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Code review</t>
+          <t xml:space="preserve">Лекция 13. Тестирование ПО</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,19 +735,19 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ревью ловит дефекты раньше тестов и распространяет знание по команде. Разберём порядок просмотра, размер изменения и тон замечаний.</t>
+          <t xml:space="preserve">Тестирование показывает наличие дефектов, но не доказывает их отсутствие. Разберём уровни, виды и пирамиду тестов, а также когда нужен ручной прогон.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ревью, пул-реквест, замечание, чек-лист, размер изменения</t>
+          <t xml:space="preserve">уровень тестирования, регрессия, пирамида тестов, тест-план, дефект</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23-24</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Отладка</t>
+          <t xml:space="preserve">Практика 7. Тест-кейсы; Автоматизация проверок</t>
         </is>
       </c>
       <c r="D25" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ищете причину падения программы по трассировке и точкам останова, проверяете гипотезы. Сдаёте исправленный код и разбор причины дефекта.</t>
+          <t xml:space="preserve">Пишете тест-кейсы на функцию и превращаете часть из них в автотесты с проверкой результата. Сдаёте набор тест-кейсов и запускаемый набор тестов.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">трассировка, точка останова, гипотеза, воспроизведение, лог</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t xml:space="preserve">тест-кейс, граничное значение, автотест, assert, покрытие</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Тестирование ПО</t>
+          <t xml:space="preserve">Лекция 14. Отладка</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование показывает наличие дефектов, но не доказывает их отсутствие. Разберём уровни, виды и пирамиду тестов, а также когда нужен ручной прогон.</t>
+          <t xml:space="preserve">Отладка начинается с устойчивого воспроизведения дефекта, а не с правки кода. Разберём бинарный поиск причины, логирование и типичные ловушки.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">уровень тестирования, регрессия, пирамида тестов, тест-план, дефект</t>
+          <t xml:space="preserve">воспроизведение, бинарный поиск, логирование, точка останова, стек вызовов</t>
         </is>
       </c>
     </row>
@@ -817,140 +817,140 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Практика 8. Отладка</t>
+        </is>
+      </c>
+      <c r="D27" s="6">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ищете причину падения программы по трассировке и точкам останова, проверяете гипотезы. Сдаёте исправленный код и разбор причины дефекта.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">трассировка, точка останова, гипотеза, воспроизведение, лог</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 15. Документирование</t>
+        </is>
+      </c>
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Документация делится на пользовательскую, эксплуатационную и внутреннюю, и у каждой свой читатель. Разберём структуру документа и поддержание его в актуальном виде.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">документация, руководство пользователя, регламент, шаблон, актуальность</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 9. Документация</t>
         </is>
       </c>
-      <c r="D27" s="6">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D29" s="6">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Оформляете документацию проекта: руководство запуска, описание API и журнал изменений. Сдаёте документ, по которому новый человек запускает проект.</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">руководство, API, docstring, журнал изменений, версия</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 14. Отладка</t>
-        </is>
-      </c>
-      <c r="D28" s="6">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Отладка начинается с устойчивого воспроизведения дефекта, а не с правки кода. Разберём бинарный поиск причины, логирование и типичные ловушки.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">воспроизведение, бинарный поиск, логирование, точка останова, стек вызовов</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 15. Документирование</t>
-        </is>
-      </c>
-      <c r="D29" s="6">
-        <v>2</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Документация делится на пользовательскую, эксплуатационную и внутреннюю, и у каждой свой читатель. Разберём структуру документа и поддержание его в актуальном виде.</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">документация, руководство пользователя, регламент, шаблон, актуальность</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-30</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Сборка проекта; Релиз</t>
+          <t xml:space="preserve">Лекция 16. Сборка и релиз</t>
         </is>
       </c>
       <c r="D30" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настраиваете сборку проекта, прогоняете проверки и выпускаете версию с тегом и журналом изменений. Сдаёте собранный артефакт и описание релиза.</t>
+          <t xml:space="preserve">Сборка превращает исходники в готовый артефакт, релиз закрепляет версию и доводит её до пользователя. Разберём версионирование, конвейер и откат.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сборка, зависимости, версия, тег, артефакт, журнал изменений</t>
+          <t xml:space="preserve">конвейер, семантическое версионирование, артефакт, тег, откат</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">30-31</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Сборка и релиз</t>
+          <t xml:space="preserve">Практика 10. Сборка проекта; Релиз</t>
         </is>
       </c>
       <c r="D31" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сборка превращает исходники в готовый артефакт, релиз закрепляет версию и доводит её до пользователя. Разберём версионирование, конвейер и откат.</t>
+          <t xml:space="preserve">Настраиваете сборку проекта, прогоняете проверки и выпускаете версию с тегом и журналом изменений. Сдаёте собранный артефакт и описание релиза.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">конвейер, семантическое версионирование, артефакт, тег, откат</t>
+          <t xml:space="preserve">сборка, зависимости, версия, тег, артефакт, журнал изменений</t>
         </is>
       </c>
     </row>
@@ -984,67 +984,67 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33-34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 18. Сопровождение</t>
+        </is>
+      </c>
+      <c r="D33" s="6">
+        <v>2</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сопровождение охватывает исправления, доработки и поддержку пользователей после сдачи. Разберём классификацию обращений, приоритеты и метрики службы поддержки.</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">сопровождение, обращение, SLA, приоритет, регрессия, релиз</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34-35</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 11. Внедрение; Сопровождение</t>
         </is>
       </c>
-      <c r="D33" s="6">
+      <c r="D34" s="6">
         <v>4</v>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Разворачиваете систему на стенде, переносите данные и оформляете регламент сопровождения. Сдаёте работающий стенд, план миграции и инструкцию.</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">развёртывание, миграция, регламент, обращение, резервная копия</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 18. Сопровождение</t>
-        </is>
-      </c>
-      <c r="D34" s="6">
-        <v>2</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сопровождение охватывает исправления, доработки и поддержку пользователей после сдачи. Разберём классификацию обращений, приоритеты и метрики службы поддержки.</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">сопровождение, обращение, SLA, приоритет, регрессия, релиз</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1052,55 +1052,55 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 19. Оценка качества и рисков</t>
+        </is>
+      </c>
+      <c r="D35" s="6">
+        <v>2</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Качество измеряют метриками продукта и процесса, а риски оценивают по вероятности и последствиям. Разберём реестр рисков и выбор мер.</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">метрика, риск, вероятность, реестр рисков, технический долг</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 12. Оценка качества</t>
         </is>
       </c>
-      <c r="D35" s="6">
-        <v>2</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D36" s="6">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Оцениваете учебный проект по метрикам качества и находите слабые места в коде и документации. Сдаёте отчёт с метриками, дефектами и планом улучшений.</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">метрика, сложность, дублирование, чек-лист, технический долг</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 19. Оценка качества и рисков</t>
-        </is>
-      </c>
-      <c r="D36" s="6">
-        <v>2</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Качество измеряют метриками продукта и процесса, а риски оценивают по вероятности и последствиям. Разберём реестр рисков и выбор мер.</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">метрика, риск, вероятность, реестр рисков, технический долг</t>
         </is>
       </c>
     </row>
